--- a/cases/AConly_case14.xlsx
+++ b/cases/AConly_case14.xlsx
@@ -2832,7 +2832,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
         <v>1e-06</v>
@@ -2879,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
         <v>1e-06</v>
@@ -2926,7 +2926,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
         <v>1e-06</v>
@@ -2973,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
         <v>1e-06</v>
@@ -3020,7 +3020,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
         <v>1e-06</v>
